--- a/20260320-TAKA00003-IMEI.xlsx
+++ b/20260320-TAKA00003-IMEI.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F78C8D22-2FDC-42E9-B035-2B608CA93E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34DEEEF-E2C0-4A4F-AECE-F5E656BF9C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="230">
   <si>
     <t>Terminal Serial</t>
   </si>
@@ -662,16 +662,70 @@
   </si>
   <si>
     <t>865778075500798</t>
+  </si>
+  <si>
+    <t>BP029089</t>
+  </si>
+  <si>
+    <t>BP029146</t>
+  </si>
+  <si>
+    <t>BP029490</t>
+  </si>
+  <si>
+    <t>BP029797</t>
+  </si>
+  <si>
+    <t>6285115453938</t>
+  </si>
+  <si>
+    <t>6285197937121</t>
+  </si>
+  <si>
+    <t>6285115453942</t>
+  </si>
+  <si>
+    <t>6285115453931</t>
+  </si>
+  <si>
+    <t>865778079936881</t>
+  </si>
+  <si>
+    <t>865778079929605</t>
+  </si>
+  <si>
+    <t>865778079924929</t>
+  </si>
+  <si>
+    <t>865778079933821</t>
+  </si>
+  <si>
+    <t>B1677HZO</t>
+  </si>
+  <si>
+    <t>B1252HZL</t>
+  </si>
+  <si>
+    <t>B1679HZO</t>
+  </si>
+  <si>
+    <t>B1250HZL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1005,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.140625" style="1"/>
@@ -1912,12 +1966,81 @@
         <v>8</v>
       </c>
     </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>214</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D54" t="s">
+        <v>226</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D55" t="s">
+        <v>227</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D56" t="s">
+        <v>228</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D57" t="s">
+        <v>229</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E54">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
